--- a/data/trans_orig/P59A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P59A-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si viven actualmente en pareja en 2007</t>
+          <t>Población según si viven actualmente en pareja en 2007 (tasa de respuesta: 98,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18474</t>
+          <t>18030</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>38671</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31496</t>
+          <t>31303</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57105</t>
+          <t>55917</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>56022</t>
+          <t>55951</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>88607</t>
+          <t>86188</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>424225</t>
+          <t>423759</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>443956</t>
+          <t>444400</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>376153</t>
+          <t>377341</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>401762</t>
+          <t>401955</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>807081</t>
+          <t>809500</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>839666</t>
+          <t>839737</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88303</t>
+          <t>88512</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>126135</t>
+          <t>123745</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62774</t>
+          <t>64393</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>94614</t>
+          <t>96482</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>161749</t>
+          <t>160915</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>212946</t>
+          <t>208133</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>28,87%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>315894</t>
+          <t>318284</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>353726</t>
+          <t>353517</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>184345</t>
+          <t>182477</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>216185</t>
+          <t>214566</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>508042</t>
+          <t>512855</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>559239</t>
+          <t>560073</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,68%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9004</t>
+          <t>9174</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25202</t>
+          <t>24040</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9409</t>
+          <t>9142</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24842</t>
+          <t>24908</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21990</t>
+          <t>21371</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45222</t>
+          <t>44327</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,74%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>112997</t>
+          <t>114159</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>129195</t>
+          <t>129025</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>101800</t>
+          <t>101734</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>117233</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>219619</t>
+          <t>220514</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>242851</t>
+          <t>243470</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,93%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9111</t>
+          <t>10315</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26156</t>
+          <t>25556</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6702</t>
+          <t>6099</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11031</t>
+          <t>11480</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29056</t>
+          <t>28720</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,9%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63688</t>
+          <t>64288</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>80733</t>
+          <t>79529</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>96241</t>
+          <t>96844</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>163731</t>
+          <t>164067</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>181756</t>
+          <t>181307</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,05%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2809</t>
+          <t>2670</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13019</t>
+          <t>13204</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>945</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7914</t>
+          <t>8459</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5268</t>
+          <t>4739</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17438</t>
+          <t>17082</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39652</t>
+          <t>39467</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>49862</t>
+          <t>50001</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>83357</t>
+          <t>82812</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>90324</t>
+          <t>90326</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>126504</t>
+          <t>126860</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>138674</t>
+          <t>139203</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,71%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4265</t>
+          <t>4355</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,62 +2483,62 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>838</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1770</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>5065</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>838</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>5080</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33076</t>
+          <t>32986</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>129282</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>131052</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>163312</t>
+          <t>163327</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>7527</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,62 +2826,62 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>1834</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2191</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>5575</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1834</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>6644</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>59592</t>
+          <t>58212</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>215947</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>218138</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>277233</t>
+          <t>278302</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>151556</t>
+          <t>152374</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>204574</t>
+          <t>203455</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>118904</t>
+          <t>118514</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>164076</t>
+          <t>167653</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>281649</t>
+          <t>284463</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>352236</t>
+          <t>353780</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1083678</t>
+          <t>1084797</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1136696</t>
+          <t>1135878</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1218187</t>
+          <t>1214610</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1263359</t>
+          <t>1263749</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2318279</t>
+          <t>2316735</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2388866</t>
+          <t>2386052</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,35%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si viven actualmente en pareja en 2012</t>
+          <t>Población según si viven actualmente en pareja en 2012 (tasa de respuesta: 97,56%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24307</t>
+          <t>24300</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45699</t>
+          <t>46573</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32090</t>
+          <t>32432</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57619</t>
+          <t>57181</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60795</t>
+          <t>61140</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95451</t>
+          <t>95440</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>381640</t>
+          <t>380766</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>403032</t>
+          <t>403039</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>325906</t>
+          <t>326344</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>351435</t>
+          <t>351093</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>715413</t>
+          <t>715424</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>750069</t>
+          <t>749724</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,46%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>86854</t>
+          <t>88071</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>124870</t>
+          <t>124649</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>70833</t>
+          <t>70305</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>102068</t>
+          <t>103542</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>164368</t>
+          <t>165982</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>214097</t>
+          <t>215593</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,28%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>331965</t>
+          <t>332186</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>369981</t>
+          <t>368764</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>177416</t>
+          <t>175942</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>208651</t>
+          <t>209179</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>522222</t>
+          <t>520726</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>571951</t>
+          <t>570337</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,46%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25267</t>
+          <t>25949</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48893</t>
+          <t>50324</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33350</t>
+          <t>33147</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58993</t>
+          <t>57680</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66648</t>
+          <t>66094</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>101456</t>
+          <t>99342</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>32,4%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>115297</t>
+          <t>113866</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>138923</t>
+          <t>138241</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>83383</t>
+          <t>84696</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>109026</t>
+          <t>109229</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>205109</t>
+          <t>207223</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>239917</t>
+          <t>240471</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,44%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16117</t>
+          <t>16811</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36960</t>
+          <t>37960</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5964</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20747</t>
+          <t>20185</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25265</t>
+          <t>25458</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51667</t>
+          <t>52123</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,2%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>102813</t>
+          <t>101813</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>123656</t>
+          <t>122962</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>110899</t>
+          <t>111461</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>125682</t>
+          <t>126434</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>219751</t>
+          <t>219295</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>246153</t>
+          <t>245960</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,62%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3139</t>
+          <t>3092</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15295</t>
+          <t>14618</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6119</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19245</t>
+          <t>19385</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11359</t>
+          <t>10699</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29203</t>
+          <t>29275</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,88%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46191</t>
+          <t>46868</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>58347</t>
+          <t>58394</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>83004</t>
+          <t>82864</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>96130</t>
+          <t>96076</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>134531</t>
+          <t>134459</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>152375</t>
+          <t>153035</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,47%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>925</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7962</t>
+          <t>7782</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>962</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10684</t>
+          <t>10034</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14152</t>
+          <t>14480</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>48755</t>
+          <t>48935</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>55767</t>
+          <t>55792</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>134544</t>
+          <t>135194</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>144256</t>
+          <t>144266</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>187793</t>
+          <t>187465</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>199019</t>
+          <t>199926</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -5770,97 +5770,97 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>2097</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>2077</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>6377</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>2097</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>7401</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>6383</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>2097</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>7392</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>74924</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>77001</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>231876</t>
+          <t>232900</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>308886</t>
+          <t>309895</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>187924</t>
+          <t>185313</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>245821</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>177179</t>
+          <t>176522</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>229468</t>
+          <t>230592</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>374364</t>
+          <t>375886</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>452819</t>
+          <t>456788</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1137519</t>
+          <t>1141846</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1195416</t>
+          <t>1198027</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1194315</t>
+          <t>1193191</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1246604</t>
+          <t>1247261</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2354304</t>
+          <t>2350335</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2432759</t>
+          <t>2431237</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,61%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si viven actualmente en pareja en 2016</t>
+          <t>Población según si viven actualmente en pareja en 2016 (tasa de respuesta: 97,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16670</t>
+          <t>16687</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36386</t>
+          <t>36949</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37175</t>
+          <t>36304</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>61813</t>
+          <t>62303</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59169</t>
+          <t>60289</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>92169</t>
+          <t>92522</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>359561</t>
+          <t>358998</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>379277</t>
+          <t>379260</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>295919</t>
+          <t>295429</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>320557</t>
+          <t>321428</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>661510</t>
+          <t>661157</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>694510</t>
+          <t>693390</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,0%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>108585</t>
+          <t>106670</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>144525</t>
+          <t>145162</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>82689</t>
+          <t>82917</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>114041</t>
+          <t>114373</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>202452</t>
+          <t>201466</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>252183</t>
+          <t>248477</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>35,31%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>241530</t>
+          <t>240893</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>277470</t>
+          <t>279385</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>203626</t>
+          <t>203294</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>234978</t>
+          <t>234750</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>451540</t>
+          <t>455246</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>501271</t>
+          <t>502257</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,37%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41896</t>
+          <t>41247</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>69095</t>
+          <t>69197</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36980</t>
+          <t>37312</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61111</t>
+          <t>61596</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>87369</t>
+          <t>85483</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>123361</t>
+          <t>121930</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,15%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>152325</t>
+          <t>152223</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>179524</t>
+          <t>180173</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>121909</t>
+          <t>121424</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>146040</t>
+          <t>145708</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>66,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>281078</t>
+          <t>282509</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>317070</t>
+          <t>318956</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,86%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15184</t>
+          <t>14351</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35231</t>
+          <t>34789</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10039</t>
+          <t>10436</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27496</t>
+          <t>28426</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31275</t>
+          <t>29509</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>57021</t>
+          <t>55227</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>149622</t>
+          <t>150064</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>169669</t>
+          <t>170502</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>146375</t>
+          <t>145445</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>163832</t>
+          <t>163435</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>301703</t>
+          <t>303497</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>327449</t>
+          <t>329215</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,77%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10666</t>
+          <t>10589</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28402</t>
+          <t>27622</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3581</t>
+          <t>3574</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16811</t>
+          <t>16520</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16501</t>
+          <t>17482</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39236</t>
+          <t>38920</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>78623</t>
+          <t>79403</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>96359</t>
+          <t>96436</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>154323</t>
+          <t>154614</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>167553</t>
+          <t>167560</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>238923</t>
+          <t>239239</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>261658</t>
+          <t>260677</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,72%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>1841</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10382</t>
+          <t>11004</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1892</t>
+          <t>1869</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10990</t>
+          <t>10549</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>66134</t>
+          <t>65512</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>74656</t>
+          <t>74675</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>143328</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>145348</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>210874</t>
+          <t>211315</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>219972</t>
+          <t>219995</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -8754,7 +8754,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7840</t>
+          <t>7279</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10409</t>
+          <t>10466</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8804,7 +8804,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>832</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13544</t>
+          <t>13274</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -8862,7 +8862,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>82287</t>
+          <t>82848</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>233934</t>
+          <t>233877</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>320926</t>
+          <t>321196</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>333157</t>
+          <t>333638</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>227296</t>
+          <t>227067</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>286069</t>
+          <t>287809</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>197988</t>
+          <t>197057</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>253637</t>
+          <t>255272</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>438777</t>
+          <t>441393</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>521238</t>
+          <t>522749</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,11%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1175873</t>
+          <t>1174133</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1234646</t>
+          <t>1234875</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1339478</t>
+          <t>1337843</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1395127</t>
+          <t>1396058</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2533820</t>
+          <t>2532309</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2616281</t>
+          <t>2613665</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,55%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si viven actualmente en pareja en 2023</t>
+          <t>Población según si viven actualmente en pareja en 2023 (tasa de respuesta: 99,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7925</t>
+          <t>8314</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34826</t>
+          <t>39781</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12840</t>
+          <t>13546</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37448</t>
+          <t>38997</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24982</t>
+          <t>25965</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63077</t>
+          <t>63985</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>363823</t>
+          <t>358868</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>390724</t>
+          <t>390335</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>264287</t>
+          <t>262738</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>288895</t>
+          <t>288189</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>637307</t>
+          <t>636399</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>675402</t>
+          <t>674419</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,29%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83122</t>
+          <t>82469</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>128409</t>
+          <t>127938</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47995</t>
+          <t>46033</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>119444</t>
+          <t>115929</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>137993</t>
+          <t>140595</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>229309</t>
+          <t>231661</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,98%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>216048</t>
+          <t>216519</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>261335</t>
+          <t>261988</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>238451</t>
+          <t>241966</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>309900</t>
+          <t>311862</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>473044</t>
+          <t>470692</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>564360</t>
+          <t>561758</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>79,98%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>51494</t>
+          <t>52163</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>79983</t>
+          <t>79914</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>51719</t>
+          <t>49857</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73738</t>
+          <t>73158</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>110079</t>
+          <t>111512</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>147046</t>
+          <t>148453</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,75%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>144848</t>
+          <t>144917</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>173337</t>
+          <t>172668</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>116703</t>
+          <t>117283</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>138722</t>
+          <t>140584</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>268226</t>
+          <t>266819</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>305193</t>
+          <t>303760</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,15%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21325</t>
+          <t>21401</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42369</t>
+          <t>42642</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25843</t>
+          <t>26310</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43166</t>
+          <t>43482</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51838</t>
+          <t>51944</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>79090</t>
+          <t>80634</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,63%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>213806</t>
+          <t>213533</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>234850</t>
+          <t>234774</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>158124</t>
+          <t>157808</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>175447</t>
+          <t>174980</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>378376</t>
+          <t>376832</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>405628</t>
+          <t>405522</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,65%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14869</t>
+          <t>15270</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33592</t>
+          <t>34370</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10359</t>
+          <t>10275</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21689</t>
+          <t>21075</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28048</t>
+          <t>28725</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50513</t>
+          <t>50334</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,68%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>161076</t>
+          <t>160298</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>179799</t>
+          <t>179398</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>180739</t>
+          <t>181353</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>192069</t>
+          <t>192153</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>346583</t>
+          <t>346762</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>369048</t>
+          <t>368371</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,77%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4674</t>
+          <t>4680</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13438</t>
+          <t>13468</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2199</t>
+          <t>2212</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8659</t>
+          <t>8178</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8122</t>
+          <t>8188</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18476</t>
+          <t>18629</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>95376</t>
+          <t>95346</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>104140</t>
+          <t>104134</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>173263</t>
+          <t>173744</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>179723</t>
+          <t>179710</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>272259</t>
+          <t>272106</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>282613</t>
+          <t>282547</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,18%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3382</t>
+          <t>3490</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11656</t>
+          <t>11784</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>659</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4617</t>
+          <t>4756</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5083</t>
+          <t>4910</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14633</t>
+          <t>14583</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>90338</t>
+          <t>90210</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>98612</t>
+          <t>98504</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>311860</t>
+          <t>311721</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>315783</t>
+          <t>315818</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>403838</t>
+          <t>403888</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>413388</t>
+          <t>413561</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>224744</t>
+          <t>223772</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>295040</t>
+          <t>297705</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>193613</t>
+          <t>195437</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>261573</t>
+          <t>260487</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>440373</t>
+          <t>439869</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>543579</t>
+          <t>536616</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,87%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1334548</t>
+          <t>1331883</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1404844</t>
+          <t>1405816</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1490616</t>
+          <t>1491702</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1558576</t>
+          <t>1556752</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2838198</t>
+          <t>2845161</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2941404</t>
+          <t>2941908</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>86,99%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P59A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P59A-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18030</t>
+          <t>18023</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38671</t>
+          <t>38096</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31303</t>
+          <t>31655</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55917</t>
+          <t>57091</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55951</t>
+          <t>54633</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86188</t>
+          <t>86129</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>423759</t>
+          <t>424334</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>444400</t>
+          <t>444407</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>377341</t>
+          <t>376167</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>401955</t>
+          <t>401603</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>809500</t>
+          <t>809559</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>839737</t>
+          <t>841055</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,9%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88512</t>
+          <t>89618</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>123745</t>
+          <t>128804</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>64393</t>
+          <t>62743</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>96482</t>
+          <t>92317</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>160915</t>
+          <t>161862</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>208133</t>
+          <t>210302</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>29,17%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>318284</t>
+          <t>313225</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>353517</t>
+          <t>352411</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>182477</t>
+          <t>186642</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>214566</t>
+          <t>216216</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>512855</t>
+          <t>510686</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>560073</t>
+          <t>559126</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,55%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9174</t>
+          <t>9346</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24040</t>
+          <t>24047</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9142</t>
+          <t>8480</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24908</t>
+          <t>24552</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21371</t>
+          <t>21837</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44327</t>
+          <t>42861</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,18%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>114159</t>
+          <t>114152</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>129025</t>
+          <t>128853</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>101734</t>
+          <t>102090</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>118162</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>220514</t>
+          <t>221980</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>243470</t>
+          <t>243004</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,75%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10315</t>
+          <t>9995</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25556</t>
+          <t>25547</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6099</t>
+          <t>7144</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11480</t>
+          <t>11137</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28720</t>
+          <t>28659</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,87%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>64288</t>
+          <t>64297</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>79529</t>
+          <t>79849</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>96844</t>
+          <t>95799</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>164067</t>
+          <t>164128</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>181307</t>
+          <t>181650</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,22%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2827</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13204</t>
+          <t>13424</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>955</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8459</t>
+          <t>8057</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4739</t>
+          <t>5106</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17082</t>
+          <t>17556</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,2%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39467</t>
+          <t>39247</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>50001</t>
+          <t>49844</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>82812</t>
+          <t>83214</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>90326</t>
+          <t>90316</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>126860</t>
+          <t>126386</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>139203</t>
+          <t>138836</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,45%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4355</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5065</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32986</t>
+          <t>33014</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>163327</t>
+          <t>164141</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7527</t>
+          <t>5698</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5575</t>
+          <t>6382</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>58212</t>
+          <t>60041</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>278302</t>
+          <t>277495</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>152374</t>
+          <t>152328</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>203455</t>
+          <t>203813</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>118514</t>
+          <t>119166</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>167653</t>
+          <t>166694</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>284463</t>
+          <t>284529</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>353780</t>
+          <t>357341</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1084797</t>
+          <t>1084439</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1135878</t>
+          <t>1135924</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1214610</t>
+          <t>1215569</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1263749</t>
+          <t>1263097</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2316735</t>
+          <t>2313174</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2386052</t>
+          <t>2385986</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24300</t>
+          <t>23958</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46573</t>
+          <t>45240</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32432</t>
+          <t>32593</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57181</t>
+          <t>56041</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>61140</t>
+          <t>61068</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95440</t>
+          <t>94439</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,65%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>380766</t>
+          <t>382099</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>403039</t>
+          <t>403381</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>326344</t>
+          <t>327484</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>351093</t>
+          <t>350932</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>715424</t>
+          <t>716425</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>749724</t>
+          <t>749796</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,47%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88071</t>
+          <t>86293</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>124649</t>
+          <t>123939</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>70305</t>
+          <t>69750</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>103542</t>
+          <t>101155</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>165982</t>
+          <t>167273</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>215593</t>
+          <t>216226</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,37%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>332186</t>
+          <t>332896</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>368764</t>
+          <t>370542</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>175942</t>
+          <t>178329</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>209179</t>
+          <t>209734</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>520726</t>
+          <t>520093</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>570337</t>
+          <t>569046</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,28%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25949</t>
+          <t>26953</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50324</t>
+          <t>49745</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33147</t>
+          <t>33299</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57680</t>
+          <t>57828</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66094</t>
+          <t>64620</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>99342</t>
+          <t>99073</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,32%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>113866</t>
+          <t>114445</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>138241</t>
+          <t>137237</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>84696</t>
+          <t>84548</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>109229</t>
+          <t>109077</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>207223</t>
+          <t>207492</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>240471</t>
+          <t>241945</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,92%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16811</t>
+          <t>16991</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37960</t>
+          <t>38193</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20185</t>
+          <t>20870</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25458</t>
+          <t>25927</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52123</t>
+          <t>51933</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,13%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>101813</t>
+          <t>101580</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>122962</t>
+          <t>122782</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>111461</t>
+          <t>110776</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>126434</t>
+          <t>126360</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>219295</t>
+          <t>219485</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>245960</t>
+          <t>245491</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,45%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3092</t>
+          <t>3120</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14618</t>
+          <t>15641</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>6060</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19385</t>
+          <t>19853</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10699</t>
+          <t>11345</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29275</t>
+          <t>29258</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,87%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46868</t>
+          <t>45845</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>58394</t>
+          <t>58366</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>82864</t>
+          <t>82396</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>96076</t>
+          <t>96189</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>134459</t>
+          <t>134476</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>153035</t>
+          <t>152389</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,07%</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7782</t>
+          <t>7741</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>971</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10034</t>
+          <t>11508</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14480</t>
+          <t>14766</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>48935</t>
+          <t>48976</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>135194</t>
+          <t>133720</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>144266</t>
+          <t>144257</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>187465</t>
+          <t>187179</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>199926</t>
+          <t>199928</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6377</t>
+          <t>8073</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6383</t>
+          <t>6390</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>232900</t>
+          <t>231204</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>309895</t>
+          <t>309888</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>185313</t>
+          <t>184121</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>241494</t>
+          <t>238355</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>176522</t>
+          <t>174290</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>230592</t>
+          <t>233501</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>375886</t>
+          <t>373746</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>456788</t>
+          <t>452634</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,12%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1141846</t>
+          <t>1144985</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1198027</t>
+          <t>1199219</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1193191</t>
+          <t>1190282</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1247261</t>
+          <t>1249493</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2350335</t>
+          <t>2354489</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2431237</t>
+          <t>2433377</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,69%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16687</t>
+          <t>17230</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36949</t>
+          <t>39110</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36304</t>
+          <t>37392</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>62303</t>
+          <t>62395</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60289</t>
+          <t>60167</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>92522</t>
+          <t>92706</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,3%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>358998</t>
+          <t>356837</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>379260</t>
+          <t>378717</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>295429</t>
+          <t>295337</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>321428</t>
+          <t>320340</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>661157</t>
+          <t>660973</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>693390</t>
+          <t>693512</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,02%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>106670</t>
+          <t>109637</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>145162</t>
+          <t>145656</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>82917</t>
+          <t>82186</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>114373</t>
+          <t>114577</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>201466</t>
+          <t>198519</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>248477</t>
+          <t>247637</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,19%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>240893</t>
+          <t>240399</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>279385</t>
+          <t>276418</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>71,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>203294</t>
+          <t>203090</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>234750</t>
+          <t>235481</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>455246</t>
+          <t>456086</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>502257</t>
+          <t>505204</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,79%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41247</t>
+          <t>43191</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>69197</t>
+          <t>71548</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37312</t>
+          <t>38520</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61596</t>
+          <t>63326</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>85483</t>
+          <t>86027</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>121930</t>
+          <t>122614</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,32%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>152223</t>
+          <t>149872</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>180173</t>
+          <t>178229</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>121424</t>
+          <t>119694</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>145708</t>
+          <t>144500</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>282509</t>
+          <t>281825</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>318956</t>
+          <t>318412</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,73%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14351</t>
+          <t>15681</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34789</t>
+          <t>35472</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10436</t>
+          <t>10542</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28426</t>
+          <t>27160</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29509</t>
+          <t>30231</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55227</t>
+          <t>58194</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>16,22%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>150064</t>
+          <t>149381</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>170502</t>
+          <t>169172</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>145445</t>
+          <t>146711</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>163435</t>
+          <t>163329</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>303497</t>
+          <t>300530</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>329215</t>
+          <t>328493</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,57%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10589</t>
+          <t>10243</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27622</t>
+          <t>28360</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3574</t>
+          <t>3331</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16520</t>
+          <t>16131</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17482</t>
+          <t>17257</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38920</t>
+          <t>39626</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,25%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>79403</t>
+          <t>78665</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>96436</t>
+          <t>96782</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>154614</t>
+          <t>155003</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>167560</t>
+          <t>167803</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>239239</t>
+          <t>238533</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>260677</t>
+          <t>260902</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,8%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1841</t>
+          <t>1912</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11004</t>
+          <t>10151</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10549</t>
+          <t>11669</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>65512</t>
+          <t>66365</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>74675</t>
+          <t>74604</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>211315</t>
+          <t>210195</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>219995</t>
+          <t>219961</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -8754,7 +8754,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7279</t>
+          <t>6866</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10466</t>
+          <t>10680</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8804,7 +8804,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>827</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13274</t>
+          <t>12776</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8839,7 +8839,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -8862,7 +8862,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>82848</t>
+          <t>83261</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>233877</t>
+          <t>233663</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>321196</t>
+          <t>321694</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>333638</t>
+          <t>333643</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>227067</t>
+          <t>226086</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>287809</t>
+          <t>284564</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>197057</t>
+          <t>196240</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>255272</t>
+          <t>254437</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>441393</t>
+          <t>439242</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>522749</t>
+          <t>521488</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,07%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1174133</t>
+          <t>1177378</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1234875</t>
+          <t>1235856</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1337843</t>
+          <t>1338678</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1396058</t>
+          <t>1396875</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2532309</t>
+          <t>2533570</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2613665</t>
+          <t>2615816</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,62%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>18564</t>
+          <t>22204</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8314</t>
+          <t>10264</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39781</t>
+          <t>39863</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>23406</t>
+          <t>25852</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13546</t>
+          <t>15611</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38997</t>
+          <t>43060</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>41970</t>
+          <t>48055</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25965</t>
+          <t>30187</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63985</t>
+          <t>70370</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>380085</t>
+          <t>384336</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>358868</t>
+          <t>366677</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>390335</t>
+          <t>396276</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>278329</t>
+          <t>322772</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>262738</t>
+          <t>305564</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>288189</t>
+          <t>333013</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>658414</t>
+          <t>707109</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>636399</t>
+          <t>684794</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>674419</t>
+          <t>724977</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,0%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>398649</t>
+          <t>406540</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>398649</t>
+          <t>406540</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>398649</t>
+          <t>406540</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>301735</t>
+          <t>348624</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>301735</t>
+          <t>348624</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>301735</t>
+          <t>348624</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>700384</t>
+          <t>755164</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>700384</t>
+          <t>755164</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>700384</t>
+          <t>755164</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>104731</t>
+          <t>109697</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82469</t>
+          <t>86812</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>127938</t>
+          <t>135191</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>87627</t>
+          <t>96275</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46033</t>
+          <t>79126</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>115929</t>
+          <t>114890</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>192358</t>
+          <t>205971</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>140595</t>
+          <t>176505</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>231661</t>
+          <t>236053</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,98%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>239726</t>
+          <t>270073</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>216519</t>
+          <t>244579</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>261988</t>
+          <t>292958</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>64,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>270268</t>
+          <t>218717</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>241966</t>
+          <t>200102</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>311862</t>
+          <t>235866</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>509995</t>
+          <t>488790</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>470692</t>
+          <t>458708</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>561758</t>
+          <t>518256</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>74,59%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>344457</t>
+          <t>379770</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>344457</t>
+          <t>379770</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>344457</t>
+          <t>379770</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>357895</t>
+          <t>314992</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>357895</t>
+          <t>314992</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>357895</t>
+          <t>314992</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>702353</t>
+          <t>694761</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>702353</t>
+          <t>694761</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>702353</t>
+          <t>694761</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>65814</t>
+          <t>76133</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52163</t>
+          <t>61396</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>79914</t>
+          <t>92240</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>62378</t>
+          <t>71321</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49857</t>
+          <t>60662</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73158</t>
+          <t>83496</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>128192</t>
+          <t>147454</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>111512</t>
+          <t>128073</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>148453</t>
+          <t>167464</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,85%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>159017</t>
+          <t>175282</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>144917</t>
+          <t>159175</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>172668</t>
+          <t>190019</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>128063</t>
+          <t>144430</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>117283</t>
+          <t>132255</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>140584</t>
+          <t>155089</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>287080</t>
+          <t>319712</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>266819</t>
+          <t>299702</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>303760</t>
+          <t>339093</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>72,59%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>224831</t>
+          <t>251415</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>224831</t>
+          <t>251415</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>224831</t>
+          <t>251415</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>190441</t>
+          <t>215751</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>190441</t>
+          <t>215751</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>190441</t>
+          <t>215751</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>415272</t>
+          <t>467166</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>415272</t>
+          <t>467166</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>415272</t>
+          <t>467166</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>30524</t>
+          <t>32455</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21401</t>
+          <t>22257</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42642</t>
+          <t>44114</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>34121</t>
+          <t>39166</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26310</t>
+          <t>30445</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43482</t>
+          <t>48467</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>64646</t>
+          <t>71621</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51944</t>
+          <t>58314</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>80634</t>
+          <t>87338</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,76%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>225651</t>
+          <t>237390</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>213533</t>
+          <t>225731</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>234774</t>
+          <t>247588</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>167169</t>
+          <t>182850</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>157808</t>
+          <t>173549</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>174980</t>
+          <t>191571</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>392820</t>
+          <t>420240</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>376832</t>
+          <t>404523</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>405522</t>
+          <t>433547</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,14%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>256175</t>
+          <t>269845</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>256175</t>
+          <t>269845</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>256175</t>
+          <t>269845</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>201290</t>
+          <t>222016</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>201290</t>
+          <t>222016</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>201290</t>
+          <t>222016</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>457466</t>
+          <t>491861</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>457466</t>
+          <t>491861</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>457466</t>
+          <t>491861</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>23625</t>
+          <t>25988</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15270</t>
+          <t>17941</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34370</t>
+          <t>36621</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>15096</t>
+          <t>17722</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10275</t>
+          <t>12207</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21075</t>
+          <t>24967</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>38721</t>
+          <t>43710</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28725</t>
+          <t>32652</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50334</t>
+          <t>56556</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>171043</t>
+          <t>182486</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>160298</t>
+          <t>171853</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>179398</t>
+          <t>190533</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>187332</t>
+          <t>209940</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>181353</t>
+          <t>202695</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>192153</t>
+          <t>215455</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>358375</t>
+          <t>392426</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>346762</t>
+          <t>379580</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>368371</t>
+          <t>403484</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,51%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>194668</t>
+          <t>208474</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>194668</t>
+          <t>208474</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>194668</t>
+          <t>208474</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>202428</t>
+          <t>227662</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>202428</t>
+          <t>227662</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>202428</t>
+          <t>227662</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>397096</t>
+          <t>436136</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>397096</t>
+          <t>436136</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>397096</t>
+          <t>436136</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8420</t>
+          <t>11055</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>6536</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13468</t>
+          <t>18251</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4430</t>
+          <t>4705</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2212</t>
+          <t>2052</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8178</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>12849</t>
+          <t>15760</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8188</t>
+          <t>9604</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18629</t>
+          <t>22481</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>7,04%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>100394</t>
+          <t>110263</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>95346</t>
+          <t>103067</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>104134</t>
+          <t>114782</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>177492</t>
+          <t>193344</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>173744</t>
+          <t>189906</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>179710</t>
+          <t>195997</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>277886</t>
+          <t>303607</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>272106</t>
+          <t>296886</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>282547</t>
+          <t>309763</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>96,99%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>108814</t>
+          <t>121318</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>108814</t>
+          <t>121318</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>108814</t>
+          <t>121318</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>181922</t>
+          <t>198049</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>181922</t>
+          <t>198049</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>181922</t>
+          <t>198049</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>290735</t>
+          <t>319367</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>290735</t>
+          <t>319367</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>290735</t>
+          <t>319367</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>6828</t>
+          <t>7668</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3490</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11784</t>
+          <t>13203</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>2646</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4756</t>
+          <t>6639</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>8768</t>
+          <t>10313</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4910</t>
+          <t>5860</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14583</t>
+          <t>16994</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>95166</t>
+          <t>103999</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>90210</t>
+          <t>98464</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>98504</t>
+          <t>107714</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>314538</t>
+          <t>341507</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>311721</t>
+          <t>337514</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>315818</t>
+          <t>343124</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>409703</t>
+          <t>445507</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>403888</t>
+          <t>438826</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>413561</t>
+          <t>449960</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>101994</t>
+          <t>111667</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>101994</t>
+          <t>111667</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>101994</t>
+          <t>111667</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>316477</t>
+          <t>344153</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>316477</t>
+          <t>344153</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>316477</t>
+          <t>344153</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>418471</t>
+          <t>455820</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>418471</t>
+          <t>455820</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>418471</t>
+          <t>455820</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>258506</t>
+          <t>285198</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>223772</t>
+          <t>249020</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>297705</t>
+          <t>325349</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>228998</t>
+          <t>257687</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>195437</t>
+          <t>228445</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>260487</t>
+          <t>283176</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>487504</t>
+          <t>542885</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>439869</t>
+          <t>499586</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>536616</t>
+          <t>595084</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,44%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1371082</t>
+          <t>1463829</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1331883</t>
+          <t>1423678</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1405816</t>
+          <t>1500007</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1523191</t>
+          <t>1613560</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1491702</t>
+          <t>1588071</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1556752</t>
+          <t>1642802</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2894273</t>
+          <t>3077389</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2845161</t>
+          <t>3025190</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2941908</t>
+          <t>3120688</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,2%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1629588</t>
+          <t>1749027</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1629588</t>
+          <t>1749027</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1629588</t>
+          <t>1749027</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1752189</t>
+          <t>1871247</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1752189</t>
+          <t>1871247</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1752189</t>
+          <t>1871247</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>3381777</t>
+          <t>3620274</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>3381777</t>
+          <t>3620274</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>3381777</t>
+          <t>3620274</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
